--- a/cet4/result/07_校园修仙_最强女帝系统/07_校园修仙_最强女帝系统_学习版.xlsx
+++ b/cet4/result/07_校园修仙_最强女帝系统/07_校园修仙_最强女帝系统_学习版.xlsx
@@ -397,787 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>active</v>
       </c>
       <c r="B2" t="str">
-        <v>active</v>
+        <v>/ˈæktɪv/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>积极的</v>
       </c>
-      <c r="D2" t="str">
-        <v>active(积极的)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>researcher</v>
       </c>
       <c r="B3" t="str">
-        <v>researcher</v>
+        <v>/rɪˈsɜːtʃə(r)/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>研究员</v>
       </c>
-      <c r="D3" t="str">
-        <v>researcher(研究员)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>book</v>
       </c>
       <c r="B4" t="str">
-        <v>book</v>
+        <v>/bʊk/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D4" t="str">
         <v>书</v>
       </c>
-      <c r="D4" t="str">
-        <v>book(书)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>lightning</v>
       </c>
       <c r="B5" t="str">
-        <v>lightning</v>
+        <v>/ˈlaɪtnɪŋ/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>闪电</v>
       </c>
-      <c r="D5" t="str">
-        <v>lightning(闪电)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>directly</v>
       </c>
       <c r="B6" t="str">
-        <v>directly</v>
+        <v>/dəˈrektli/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./adv./conj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>直接地</v>
       </c>
-      <c r="D6" t="str">
-        <v>directly(直接地)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>catch</v>
       </c>
       <c r="B7" t="str">
-        <v>catch</v>
+        <v>/kætʃ,ketʃ/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>抓住</v>
       </c>
-      <c r="D7" t="str">
-        <v>catch(抓住)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>base</v>
       </c>
       <c r="B8" t="str">
-        <v>base</v>
+        <v>/beɪs/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>基础</v>
       </c>
-      <c r="D8" t="str">
-        <v>base(基础)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>ability</v>
       </c>
       <c r="B9" t="str">
-        <v>ability</v>
+        <v>/əˈbɪləti/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>能力</v>
       </c>
-      <c r="D9" t="str">
-        <v>ability(能力)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>fact</v>
       </c>
       <c r="B10" t="str">
-        <v>fact</v>
+        <v>/fækt/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>事实</v>
       </c>
-      <c r="D10" t="str">
-        <v>fact(事实)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>negative</v>
       </c>
       <c r="B11" t="str">
-        <v>negative</v>
+        <v>/ˈneɡətɪv/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>消极的</v>
       </c>
-      <c r="D11" t="str">
-        <v>negative(消极的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>gray</v>
       </c>
       <c r="B12" t="str">
-        <v>gray</v>
+        <v>/ɡreɪ/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>灰色的</v>
       </c>
-      <c r="D12" t="str">
-        <v>gray(灰色的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>director</v>
       </c>
       <c r="B13" t="str">
-        <v>director</v>
+        <v>/dəˈrektə(r)/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>主任</v>
       </c>
-      <c r="D13" t="str">
-        <v>director(主任)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>promising</v>
       </c>
       <c r="B14" t="str">
-        <v>promising</v>
+        <v>/ˈprɑːmɪsɪŋ/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>有前途的</v>
       </c>
-      <c r="D14" t="str">
-        <v>promising(有前途的)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>principle</v>
       </c>
       <c r="B15" t="str">
-        <v>principle</v>
+        <v>/ˈprɪnsəpl/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>原则</v>
       </c>
-      <c r="D15" t="str">
-        <v>principle(原则)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>expand</v>
       </c>
       <c r="B16" t="str">
-        <v>expand</v>
+        <v>/ɪkˈspænd/</v>
       </c>
       <c r="C16" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D16" t="str">
         <v>扩张</v>
       </c>
-      <c r="D16" t="str">
-        <v>expand(扩张)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>defend</v>
       </c>
       <c r="B17" t="str">
-        <v>defend</v>
+        <v>/dɪˈfend/</v>
       </c>
       <c r="C17" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D17" t="str">
         <v>防护</v>
       </c>
-      <c r="D17" t="str">
-        <v>defend(防护)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>salesman</v>
       </c>
       <c r="B18" t="str">
-        <v>salesman</v>
+        <v>/ˈseɪlzmən/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>推销员</v>
       </c>
-      <c r="D18" t="str">
-        <v>salesman(推销员)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>sphere</v>
       </c>
       <c r="B19" t="str">
-        <v>sphere</v>
+        <v>/sfɪr/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>球体</v>
       </c>
-      <c r="D19" t="str">
-        <v>sphere(球体)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>immediately</v>
       </c>
       <c r="B20" t="str">
-        <v>immediately</v>
+        <v>/ɪˈmiːdiətli/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./adv./conj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>立即</v>
       </c>
-      <c r="D20" t="str">
-        <v>immediately(立即)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>hot</v>
       </c>
       <c r="B21" t="str">
-        <v>hot</v>
+        <v>/hɑːt/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D21" t="str">
         <v>热的</v>
       </c>
-      <c r="D21" t="str">
-        <v>hot(热的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>suck</v>
       </c>
       <c r="B22" t="str">
-        <v>suck</v>
+        <v>/sʌk/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D22" t="str">
         <v>吸取</v>
       </c>
-      <c r="D22" t="str">
-        <v>suck(吸取)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>combination</v>
       </c>
       <c r="B23" t="str">
-        <v>combination</v>
+        <v>/ˌkɑːmbɪˈneɪʃn/</v>
       </c>
       <c r="C23" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>结合</v>
       </c>
-      <c r="D23" t="str">
-        <v>combination(结合)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>scratch</v>
       </c>
       <c r="B24" t="str">
-        <v>scratch</v>
+        <v>/skrætʃ/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>擦伤</v>
       </c>
-      <c r="D24" t="str">
-        <v>scratch(擦伤)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>sorry</v>
       </c>
       <c r="B25" t="str">
-        <v>sorry</v>
+        <v>/ˈsɑːri/</v>
       </c>
       <c r="C25" t="str">
+        <v>adj./int.</v>
+      </c>
+      <c r="D25" t="str">
         <v>遗憾的</v>
       </c>
-      <c r="D25" t="str">
-        <v>sorry(遗憾的)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>force</v>
       </c>
       <c r="B26" t="str">
-        <v>force</v>
+        <v>/fɔːrs/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D26" t="str">
         <v>力量</v>
       </c>
-      <c r="D26" t="str">
-        <v>force(力量)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>voyage</v>
       </c>
       <c r="B27" t="str">
-        <v>voyage</v>
+        <v>/ˈvɔɪɪdʒ/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D27" t="str">
         <v>航行</v>
       </c>
-      <c r="D27" t="str">
-        <v>voyage(航行)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>temple</v>
       </c>
       <c r="B28" t="str">
-        <v>temple</v>
+        <v>/ˈtempl/</v>
       </c>
       <c r="C28" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>寺庙</v>
       </c>
-      <c r="D28" t="str">
-        <v>temple(寺庙)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>stitch</v>
       </c>
       <c r="B29" t="str">
-        <v>stitch</v>
+        <v>/stɪtʃ/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D29" t="str">
         <v>缝合</v>
       </c>
-      <c r="D29" t="str">
-        <v>stitch(缝合)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>Brazil</v>
       </c>
       <c r="B30" t="str">
-        <v>Brazil</v>
+        <v>/brəˈzɪl/</v>
       </c>
       <c r="C30" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>巴西</v>
       </c>
-      <c r="D30" t="str">
-        <v>Brazil(巴西)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>mind</v>
       </c>
       <c r="B31" t="str">
-        <v>mind</v>
+        <v>/maɪnd/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D31" t="str">
         <v>理智</v>
       </c>
-      <c r="D31" t="str">
-        <v>mind(理智)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>Atlantic</v>
       </c>
       <c r="B32" t="str">
-        <v>Atlantic</v>
+        <v>/ətˈlæntɪk/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D32" t="str">
         <v>大西洋</v>
       </c>
-      <c r="D32" t="str">
-        <v>Atlantic(大西洋)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>million</v>
       </c>
       <c r="B33" t="str">
-        <v>million</v>
+        <v>/ˈmɪljən/</v>
       </c>
       <c r="C33" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D33" t="str">
         <v>百万</v>
       </c>
-      <c r="D33" t="str">
-        <v>million(百万)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>liner</v>
       </c>
       <c r="B34" t="str">
-        <v>liner</v>
+        <v>/ˈlaɪnər/</v>
       </c>
       <c r="C34" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>班轮</v>
       </c>
-      <c r="D34" t="str">
-        <v>liner(班轮)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>electronic</v>
       </c>
       <c r="B35" t="str">
-        <v>electronic</v>
+        <v>/ɪˌlekˈtrɑːnɪk/</v>
       </c>
       <c r="C35" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D35" t="str">
         <v>电子</v>
       </c>
-      <c r="D35" t="str">
-        <v>electronic(电子)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>desire</v>
       </c>
       <c r="B36" t="str">
-        <v>desire</v>
+        <v>/dɪˈzaɪər/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D36" t="str">
         <v>欲望</v>
       </c>
-      <c r="D36" t="str">
-        <v>desire(欲望)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>associate</v>
       </c>
       <c r="B37" t="str">
-        <v>associate</v>
+        <v>/əˈsəʊsieɪt/</v>
       </c>
       <c r="C37" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D37" t="str">
         <v>联合</v>
       </c>
-      <c r="D37" t="str">
-        <v>associate(联合)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>identify</v>
       </c>
       <c r="B38" t="str">
-        <v>identify</v>
+        <v>/aɪˈdentɪfaɪ/</v>
       </c>
       <c r="C38" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D38" t="str">
         <v>识别</v>
       </c>
-      <c r="D38" t="str">
-        <v>identify(识别)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>help</v>
       </c>
       <c r="B39" t="str">
-        <v>help</v>
+        <v>/help/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D39" t="str">
         <v>帮助</v>
       </c>
-      <c r="D39" t="str">
-        <v>help(帮助)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>nearby</v>
       </c>
       <c r="B40" t="str">
-        <v>nearby</v>
+        <v>/ˌnɪrˈbaɪ/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./adj./adv./prep.</v>
+      </c>
+      <c r="D40" t="str">
         <v>附近的</v>
       </c>
-      <c r="D40" t="str">
-        <v>nearby(附近的)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>accuracy</v>
       </c>
       <c r="B41" t="str">
-        <v>accuracy</v>
+        <v>/ˈækjərəsi/</v>
       </c>
       <c r="C41" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>准确性</v>
       </c>
-      <c r="D41" t="str">
-        <v>accuracy(准确性)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>admire</v>
       </c>
       <c r="B42" t="str">
-        <v>admire</v>
+        <v>/ədˈmaɪər/</v>
       </c>
       <c r="C42" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D42" t="str">
         <v>钦佩</v>
       </c>
-      <c r="D42" t="str">
-        <v>admire(钦佩)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>besides</v>
       </c>
       <c r="B43" t="str">
-        <v>besides</v>
+        <v>/bɪˈsaɪdz/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./adv./prep.</v>
+      </c>
+      <c r="D43" t="str">
         <v>况且</v>
       </c>
-      <c r="D43" t="str">
-        <v>besides(况且)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>second</v>
       </c>
       <c r="B44" t="str">
-        <v>second</v>
+        <v>/ˈsekənd; sɪˈkɑːnd/</v>
       </c>
       <c r="C44" t="str">
+        <v>n./vt./adj./num.</v>
+      </c>
+      <c r="D44" t="str">
         <v>第二</v>
       </c>
-      <c r="D44" t="str">
-        <v>second(第二)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>lover</v>
       </c>
       <c r="B45" t="str">
-        <v>lover</v>
+        <v>/ˈlʌvər/</v>
       </c>
       <c r="C45" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>爱人</v>
       </c>
-      <c r="D45" t="str">
-        <v>lover(爱人)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>eve</v>
       </c>
       <c r="B46" t="str">
-        <v>associate</v>
+        <v>/iːv/</v>
       </c>
       <c r="C46" t="str">
-        <v>伙伴</v>
+        <v>n.</v>
       </c>
       <c r="D46" t="str">
-        <v>associate(伙伴)📢</v>
+        <v>前夕</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>prominent</v>
       </c>
       <c r="B47" t="str">
-        <v>eve</v>
+        <v>/ˈprɑːmɪnənt/</v>
       </c>
       <c r="C47" t="str">
-        <v>前夕</v>
+        <v>adj.</v>
       </c>
       <c r="D47" t="str">
-        <v>eve(前夕)📢</v>
+        <v>杰出的</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>review</v>
       </c>
       <c r="B48" t="str">
-        <v>prominent</v>
+        <v>/rɪˈvjuː/</v>
       </c>
       <c r="C48" t="str">
-        <v>杰出的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>prominent(杰出的)📢</v>
+        <v>评论</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>farmer</v>
       </c>
       <c r="B49" t="str">
-        <v>review</v>
+        <v>/ˈfɑːrmər/</v>
       </c>
       <c r="C49" t="str">
-        <v>评论</v>
+        <v>n.</v>
       </c>
       <c r="D49" t="str">
-        <v>review(评论)📢</v>
+        <v>农夫</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>mood</v>
       </c>
       <c r="B50" t="str">
-        <v>million</v>
+        <v>/muːd/</v>
       </c>
       <c r="C50" t="str">
-        <v>百万</v>
+        <v>n.</v>
       </c>
       <c r="D50" t="str">
-        <v>million(百万)📢</v>
+        <v>情绪</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>whatever</v>
       </c>
       <c r="B51" t="str">
-        <v>farmer</v>
+        <v>/wətˈevər/</v>
       </c>
       <c r="C51" t="str">
-        <v>农夫</v>
+        <v>n./adj./pron.</v>
       </c>
       <c r="D51" t="str">
-        <v>farmer(农夫)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>prominent</v>
-      </c>
-      <c r="C52" t="str">
-        <v>突出的</v>
-      </c>
-      <c r="D52" t="str">
-        <v>prominent(突出的)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>mood</v>
-      </c>
-      <c r="C53" t="str">
-        <v>情绪</v>
-      </c>
-      <c r="D53" t="str">
-        <v>mood(情绪)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>whatever</v>
-      </c>
-      <c r="C54" t="str">
         <v>无论什么</v>
-      </c>
-      <c r="D54" t="str">
-        <v>whatever(无论什么)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>gray</v>
-      </c>
-      <c r="C55" t="str">
-        <v>灰色</v>
-      </c>
-      <c r="D55" t="str">
-        <v>gray(灰色)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>